--- a/02-精益培训/05-记录追踪/03-认证进度追踪表.xlsx
+++ b/02-精益培训/05-记录追踪/03-认证进度追踪表.xlsx
@@ -110,7 +110,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -137,11 +137,20 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="001F3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -167,6 +176,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -550,7 +560,13 @@
           <t>03-认证进度追踪表</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -558,6 +574,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -565,6 +582,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -572,6 +590,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
@@ -579,6 +598,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -586,6 +606,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -593,6 +614,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
@@ -600,6 +622,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
@@ -607,6 +630,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
@@ -635,6 +659,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
@@ -642,6 +667,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
@@ -698,6 +724,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
@@ -705,6 +732,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
@@ -761,6 +789,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -768,6 +797,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
@@ -775,6 +805,7 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
@@ -782,6 +813,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
@@ -789,6 +821,7 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
@@ -796,6 +829,7 @@
         </is>
       </c>
     </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
@@ -803,6 +837,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
@@ -810,6 +845,7 @@
         </is>
       </c>
     </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
@@ -817,6 +853,7 @@
         </is>
       </c>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
@@ -824,6 +861,7 @@
         </is>
       </c>
     </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
@@ -831,6 +869,7 @@
         </is>
       </c>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
@@ -838,6 +877,7 @@
         </is>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
@@ -845,6 +885,7 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
@@ -852,6 +893,7 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
@@ -859,6 +901,7 @@
         </is>
       </c>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
@@ -866,6 +909,7 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
@@ -873,6 +917,7 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
@@ -880,6 +925,7 @@
         </is>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
@@ -908,6 +954,7 @@
         </is>
       </c>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
@@ -915,6 +962,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
@@ -943,6 +991,7 @@
         </is>
       </c>
     </row>
+    <row r="91"/>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
@@ -950,6 +999,7 @@
         </is>
       </c>
     </row>
+    <row r="93"/>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
@@ -957,6 +1007,7 @@
         </is>
       </c>
     </row>
+    <row r="95"/>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
@@ -992,6 +1043,7 @@
         </is>
       </c>
     </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
@@ -999,6 +1051,7 @@
         </is>
       </c>
     </row>
+    <row r="103"/>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
@@ -1027,6 +1080,7 @@
         </is>
       </c>
     </row>
+    <row r="108"/>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
@@ -1034,6 +1088,7 @@
         </is>
       </c>
     </row>
+    <row r="110"/>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
@@ -2291,7 +2346,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>搓丝车间</t>
+          <t>精加工车间</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
